--- a/esyluban/examples/release/DataTables/test/demo_group.xlsx
+++ b/esyluban/examples/release/DataTables/test/demo_group.xlsx
@@ -637,7 +637,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="G2:J2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -827,7 +827,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="G2:J2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -1017,7 +1017,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="G2:J2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -1207,7 +1207,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="G2:J2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -1397,7 +1397,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="G2:J2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
